--- a/research/traditional_assets/database/data/serbia/serbia_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/serbia/serbia_insurance_prop_cas.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.112</v>
+        <v>0.09519999999999999</v>
       </c>
       <c r="E2">
-        <v>1.053</v>
+        <v>0.43</v>
       </c>
       <c r="G2">
-        <v>0.1319905213270142</v>
+        <v>0.1098398169336384</v>
       </c>
       <c r="H2">
-        <v>0.1319905213270142</v>
+        <v>0.1098398169336384</v>
       </c>
       <c r="I2">
-        <v>0.1289099526066351</v>
+        <v>0.1070938215102975</v>
       </c>
       <c r="J2">
-        <v>0.1097790719840138</v>
+        <v>0.08550640552082017</v>
       </c>
       <c r="K2">
-        <v>6.11</v>
+        <v>5.06</v>
       </c>
       <c r="L2">
-        <v>0.1447867298578199</v>
+        <v>0.1157894736842105</v>
       </c>
       <c r="M2">
-        <v>0.036</v>
+        <v>0.015</v>
       </c>
       <c r="N2">
-        <v>0.006196213425129088</v>
+        <v>0.002636203866432337</v>
       </c>
       <c r="O2">
-        <v>0.005891980360065466</v>
+        <v>0.002964426877470356</v>
       </c>
       <c r="P2">
-        <v>0.036</v>
+        <v>0.015</v>
       </c>
       <c r="Q2">
-        <v>0.006196213425129088</v>
+        <v>0.002636203866432337</v>
       </c>
       <c r="R2">
-        <v>0.005891980360065466</v>
+        <v>0.002964426877470356</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -642,10 +642,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.07215626938038842</v>
+        <v>0.115746914867459</v>
       </c>
       <c r="AB2">
-        <v>0.07215626938038842</v>
+        <v>0.115746914867459</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -666,22 +666,22 @@
         <v>0</v>
       </c>
       <c r="AL2">
-        <v>0.021</v>
+        <v>0.033</v>
       </c>
       <c r="AM2">
-        <v>0.021</v>
+        <v>0.033</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>259.047619047619</v>
+        <v>141.8181818181818</v>
       </c>
       <c r="AP2">
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>259.047619047619</v>
+        <v>141.8181818181818</v>
       </c>
     </row>
     <row r="3">
@@ -701,46 +701,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.112</v>
+        <v>0.09519999999999999</v>
       </c>
       <c r="E3">
-        <v>1.053</v>
+        <v>0.43</v>
       </c>
       <c r="G3">
-        <v>0.1319905213270142</v>
+        <v>0.1098398169336384</v>
       </c>
       <c r="H3">
-        <v>0.1319905213270142</v>
+        <v>0.1098398169336384</v>
       </c>
       <c r="I3">
-        <v>0.1289099526066351</v>
+        <v>0.1070938215102975</v>
       </c>
       <c r="J3">
-        <v>0.1097790719840138</v>
+        <v>0.08550640552082017</v>
       </c>
       <c r="K3">
-        <v>6.11</v>
+        <v>5.06</v>
       </c>
       <c r="L3">
-        <v>0.1447867298578199</v>
+        <v>0.1157894736842105</v>
       </c>
       <c r="M3">
-        <v>0.036</v>
+        <v>0.015</v>
       </c>
       <c r="N3">
-        <v>0.006196213425129088</v>
+        <v>0.002636203866432337</v>
       </c>
       <c r="O3">
-        <v>0.005891980360065466</v>
+        <v>0.002964426877470356</v>
       </c>
       <c r="P3">
-        <v>0.036</v>
+        <v>0.015</v>
       </c>
       <c r="Q3">
-        <v>0.006196213425129088</v>
+        <v>0.002636203866432337</v>
       </c>
       <c r="R3">
-        <v>0.005891980360065466</v>
+        <v>0.002964426877470356</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.07215626938038842</v>
+        <v>0.115746914867459</v>
       </c>
       <c r="AB3">
-        <v>0.07215626938038842</v>
+        <v>0.115746914867459</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -779,22 +779,22 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>0.021</v>
+        <v>0.033</v>
       </c>
       <c r="AM3">
-        <v>0.021</v>
+        <v>0.033</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>259.047619047619</v>
+        <v>141.8181818181818</v>
       </c>
       <c r="AP3">
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>259.047619047619</v>
+        <v>141.8181818181818</v>
       </c>
     </row>
   </sheetData>
